--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescocompagno/Desktop/Work_Units/Codebases_to_publish/ESWC_2026_Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD34C04-252C-A04C-8B73-59328AD1037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF025235-A53A-A148-BFDB-6524F758B4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>Scenario</t>
   </si>
@@ -69,9 +69,6 @@
     <t>LLM says: "Visually check how the cables are connected between each module to verify correct polarity and ensure all required connections are secure and not swapped." So it (at least gpt4.1) does not catch on on the function of the led indicator, despite being fed explicitely the function of the led in the text input and implicitely in the electrical diagram. It has also bein clearly istructed that the cables are indistinguishable, so it is giving a meningless istruction.</t>
   </si>
   <si>
-    <t>1,1,3</t>
-  </si>
-  <si>
     <t>3 cubes - cable detached from switch</t>
   </si>
   <si>
@@ -304,6 +301,18 @@
   </si>
   <si>
     <t>All led are present on their seats on the control modules, however, only the first two are ON, the third led, and the subsequent control module leds are always OFF, irrespective of all the swith positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t>Observe -&gt; System as a whole</t>
+  </si>
+  <si>
+    <t>(Execute the action and describe the outcome)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; Clarify and observe the actual symptoms presented by the system, since the listed symptoms ([omissis]) do not specify any observable issue.</t>
   </si>
 </sst>
 </file>
@@ -701,27 +710,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
         <v>57</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -739,13 +748,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
         <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -766,13 +775,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
         <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -780,7 +789,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -790,13 +799,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -804,7 +813,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -814,13 +823,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
         <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -833,18 +842,18 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -862,97 +871,97 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
         <v>73</v>
       </c>
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
         <v>86</v>
       </c>
-      <c r="C38" t="s">
-        <v>87</v>
-      </c>
       <c r="D38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" t="s">
         <v>79</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" t="s">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>82</v>
-      </c>
-      <c r="D46" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -993,19 +1002,19 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" t="s">
-        <v>40</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -1013,7 +1022,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -1025,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1036,7 +1045,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1044,12 +1053,12 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1069,27 +1078,27 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1097,7 +1106,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1105,16 +1114,16 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
         <v>50</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1134,32 +1143,32 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
         <v>21</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>22</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
         <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1167,12 +1176,12 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1182,7 +1191,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1192,27 +1201,27 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
         <v>27</v>
       </c>
-      <c r="F26" t="s">
-        <v>28</v>
-      </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1220,20 +1229,20 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
         <v>25</v>
-      </c>
-      <c r="C28" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1248,35 +1257,35 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>35</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>36</v>
-      </c>
-      <c r="H35" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1284,16 +1293,16 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1301,16 +1310,16 @@
         <v>7</v>
       </c>
       <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
         <v>20</v>
       </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1318,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1326,7 +1335,7 @@
         <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1334,54 +1343,65 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
         <v>52</v>
       </c>
-      <c r="B43" t="s">
-        <v>53</v>
-      </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
         <v>54</v>
       </c>
-      <c r="C44" t="s">
-        <v>55</v>
+      <c r="H44" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescocompagno/Desktop/Work_Units/Codebases_to_publish/ESWC_2026_Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF025235-A53A-A148-BFDB-6524F758B4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FD5C58-66BA-7C47-BCBD-6153B5180BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
   <si>
     <t>Scenario</t>
   </si>
@@ -261,9 +261,6 @@
     <t>cable detached from switch in control x</t>
   </si>
   <si>
-    <t>The led of all the control modules are missing</t>
-  </si>
-  <si>
     <t xml:space="preserve">One of the 8 switches modules is detatched from one of the corresponding cables. To make testing more challenging all the control module leds have been removed. Fastest way to diagnose is to use the power supply led to bisect-testing the control modules. </t>
   </si>
   <si>
@@ -313,6 +310,15 @@
   </si>
   <si>
     <t xml:space="preserve">  -&gt; Clarify and observe the actual symptoms presented by the system, since the listed symptoms ([omissis]) do not specify any observable issue.</t>
+  </si>
+  <si>
+    <t>The led on the power supply module is on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the leds on the control modules are missing </t>
+  </si>
+  <si>
+    <t>The lamp does not turn on when a battery is inserted in the circuit and all the switches are in the on position</t>
   </si>
 </sst>
 </file>
@@ -698,7 +704,7 @@
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
     <col min="2" max="2" width="41.6640625" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
-    <col min="4" max="4" width="74.33203125" customWidth="1"/>
+    <col min="4" max="4" width="88.1640625" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="36.5" customWidth="1"/>
     <col min="7" max="7" width="41.33203125" customWidth="1"/>
@@ -874,10 +880,10 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -885,10 +891,10 @@
         <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -899,20 +905,20 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D35" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D36" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -920,10 +926,10 @@
         <v>72</v>
       </c>
       <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
         <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>86</v>
       </c>
       <c r="D38" t="s">
         <v>52</v>
@@ -936,32 +942,32 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" t="s">
         <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
         <v>80</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>81</v>
-      </c>
-      <c r="D46" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1034,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1356,7 +1362,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1370,7 +1376,7 @@
         <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1381,7 +1387,7 @@
         <v>54</v>
       </c>
       <c r="H44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescocompagno/Desktop/Work_Units/Codebases_to_publish/ESWC_2026_Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FD5C58-66BA-7C47-BCBD-6153B5180BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDB2889-C802-BD46-8847-E9B90184C937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="102">
   <si>
     <t>Scenario</t>
   </si>
@@ -192,9 +192,6 @@
     <t>this one was with 1 symptom: "lamp does not turn no" -&gt; {'Switch', 'Cables', 'Battery', 'MainLoad'}</t>
   </si>
   <si>
-    <t>10 cubes - detached switch in control 2</t>
-  </si>
-  <si>
     <t>The lamp does not turn on when all the switches are in the on position (that is, they are closed)</t>
   </si>
   <si>
@@ -319,6 +316,33 @@
   </si>
   <si>
     <t>The lamp does not turn on when a battery is inserted in the circuit and all the switches are in the on position</t>
+  </si>
+  <si>
+    <t>LLM Second guesses input</t>
+  </si>
+  <si>
+    <t>10 cubes - detached switch in control x</t>
+  </si>
+  <si>
+    <t>detached switch in control 3</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC_SCENARIO_RUN_2026-03-02T19:11:06</t>
+  </si>
+  <si>
+    <t>It works as intended: first some cheap tests are explored, then bisection strategy</t>
+  </si>
+  <si>
+    <t>1, 3, 3, 3(*7)</t>
+  </si>
+  <si>
+    <t>1, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3</t>
+  </si>
+  <si>
+    <t>Example of sequential search</t>
+  </si>
+  <si>
+    <t>Last one is actually 3*7 = 21… It proposes sequential search strategy, plus is inconsistent on the instruction structure</t>
   </si>
 </sst>
 </file>
@@ -716,27 +740,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -754,13 +778,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -781,13 +805,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
         <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -805,13 +829,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -829,13 +853,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
         <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -853,13 +877,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
         <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -877,97 +901,97 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
         <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" t="s">
         <v>72</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>73</v>
       </c>
-      <c r="C34" t="s">
-        <v>74</v>
-      </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
         <v>84</v>
       </c>
-      <c r="C38" t="s">
-        <v>85</v>
-      </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" t="s">
         <v>77</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" t="s">
         <v>79</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>80</v>
-      </c>
-      <c r="D46" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -987,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46E0770-1A43-B449-8786-4030E834DA3B}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="74.33203125" customWidth="1"/>
@@ -1040,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1362,51 +1386,119 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
         <v>51</v>
-      </c>
-      <c r="B43" t="s">
-        <v>52</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
         <v>53</v>
       </c>
-      <c r="C44" t="s">
-        <v>54</v>
-      </c>
       <c r="H44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
         <v>19</v>
       </c>
+      <c r="H45" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>97</v>
+      </c>
+      <c r="G50" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" t="s">
+        <v>98</v>
+      </c>
+      <c r="H51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C53" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C54" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C55" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C56" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescocompagno/Desktop/Work_Units/Codebases_to_publish/ESWC_2026_Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDB2889-C802-BD46-8847-E9B90184C937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35A89E21-5E40-A041-92DE-D76A6387CD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
+    <workbookView xWindow="14160" yWindow="1080" windowWidth="27640" windowHeight="16940" xr2:uid="{FC7576A7-5561-E04F-B1AC-279C300660B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="2" r:id="rId1"/>
     <sheet name="Notes about scenarios" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1018,7 +1019,7 @@
     <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="36.5" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" customWidth="1"/>
-    <col min="6" max="6" width="65.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
     <col min="7" max="7" width="24.1640625" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" customWidth="1"/>
     <col min="9" max="9" width="19.5" customWidth="1"/>
